--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:16</t>
+    <t xml:space="preserve">2026-09-29 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:03</t>
+    <t xml:space="preserve">2026-09-29 18:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_biobio_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_biobio_provincial.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:43</t>
+    <t xml:space="preserve">2026-10-05 04:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -521,7 +521,7 @@
         <v>34.48</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>27.02</v>
+        <v>27.03</v>
       </c>
     </row>
   </sheetData>
